--- a/templates/test-data/Visitor Test Data.xlsx
+++ b/templates/test-data/Visitor Test Data.xlsx
@@ -669,45 +669,45 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46097.73888888889</v>
+        <v>46097.35486111111</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46097.74166666667</v>
+        <v>46097.35763888889</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>fatima.khan@conestogac.on.ca</t>
+          <t>maya.patel@conestogac.on.ca</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Fatima Khan</t>
+          <t>Maya Patel</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Waterloo</t>
+          <t>Reuter</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Evening (4pm – close)</t>
+          <t>Morning (open – 12pm)</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -719,7 +719,7 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -728,7 +728,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -740,7 +740,7 @@
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -798,7 +798,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Afternoon (12 – 4pm)</t>
+          <t>Afternoon (12 – close)</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -909,7 +909,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Afternoon (12 – 4pm)</t>
+          <t>Afternoon (12 – close)</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -994,45 +994,45 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46100.56736111111</v>
+        <v>46101.74166666667</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46100.56944444445</v>
+        <v>46101.74444444444</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>fatima.khan@conestogac.on.ca</t>
+          <t>sam.rivera@conestogac.on.ca</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Fatima Khan</t>
+          <t>Sam Rivera</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Doon</t>
+          <t>Waterloo</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Afternoon (12 – 4pm)</t>
+          <t>Afternoon (12 – close)</t>
         </is>
       </c>
       <c r="H5" t="n">
         <v>9</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -1041,7 +1041,7 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -1053,7 +1053,7 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -1077,7 +1077,7 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
@@ -1089,16 +1089,12 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>Vending machine refund</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AG5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1212,54 +1208,54 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46104.82847222222</v>
+        <v>46104.7875</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46104.82986111111</v>
+        <v>46104.79027777778</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>fatima.khan@conestogac.on.ca</t>
+          <t>lucas.tremblay@conestogac.on.ca</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Fatima Khan</t>
+          <t>Lucas Tremblay</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Doon</t>
+          <t>Waterloo</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Evening (4pm – close)</t>
+          <t>Afternoon (12 – close)</t>
         </is>
       </c>
       <c r="H7" t="n">
+        <v>7</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" t="n">
         <v>4</v>
       </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1268,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1289,7 +1285,7 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -1301,7 +1297,7 @@
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -1319,19 +1315,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>46105.77847222222</v>
+        <v>46106.69652777778</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46105.78055555555</v>
+        <v>46106.7</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>sam.rivera@conestogac.on.ca</t>
+          <t>aaron.chen@conestogac.on.ca</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sam Rivera</t>
+          <t>Aaron Chen</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1341,32 +1337,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Evening (4pm – close)</t>
+          <t>Afternoon (12 – close)</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1375,16 +1371,16 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1393,7 +1389,7 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
@@ -1405,10 +1401,10 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
@@ -1426,19 +1422,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>46106.61527777778</v>
+        <v>46107.75972222222</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46106.61805555555</v>
+        <v>46107.7625</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>lucas.tremblay@conestogac.on.ca</t>
+          <t>priya.singh@conestogac.on.ca</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lucas Tremblay</t>
+          <t>Priya Singh</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1448,29 +1444,29 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Afternoon (12 – 4pm)</t>
+          <t>Afternoon (12 – close)</t>
         </is>
       </c>
       <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="n">
         <v>9</v>
       </c>
-      <c r="I9" t="n">
-        <v>7</v>
-      </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1485,7 +1481,7 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
@@ -1509,10 +1505,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1521,7 +1517,7 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -1533,45 +1529,45 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>46107.65972222222</v>
+        <v>46108.44791666666</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46107.66111111111</v>
+        <v>46108.45138888889</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>aaron.chen@conestogac.on.ca</t>
+          <t>lucas.tremblay@conestogac.on.ca</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aaron Chen</t>
+          <t>Lucas Tremblay</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Doon</t>
+          <t>Cambridge</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Afternoon (12 – 4pm)</t>
+          <t>Morning (open – 12pm)</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1583,7 +1579,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -1592,16 +1588,16 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
@@ -1619,7 +1615,7 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1631,11 +1627,11 @@
         <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>Lost &amp; found</t>
+          <t>Power outlet location</t>
         </is>
       </c>
     </row>
@@ -1644,24 +1640,24 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>46108.44791666666</v>
+        <v>46108.48333333333</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46108.45138888889</v>
+        <v>46108.48541666667</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>lucas.tremblay@conestogac.on.ca</t>
+          <t>fatima.khan@conestogac.on.ca</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lucas Tremblay</t>
+          <t>Fatima Khan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cambridge</t>
+          <t>Waterloo</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1670,16 +1666,16 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I11" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1700,10 +1696,10 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
@@ -1712,7 +1708,7 @@
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
@@ -1727,10 +1723,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1742,79 +1738,75 @@
         <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>Power outlet location</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AG11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>46108.50486111111</v>
+        <v>46111.36527777778</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46108.50625</v>
+        <v>46111.36736111111</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>priya.singh@conestogac.on.ca</t>
+          <t>sam.rivera@conestogac.on.ca</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Priya Singh</t>
+          <t>Sam Rivera</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cambridge</t>
+          <t>Doon</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Afternoon (12 – 4pm)</t>
+          <t>Morning (open – 12pm)</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="I12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
         <v>3</v>
       </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
@@ -1853,32 +1845,28 @@
         <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG12" t="inlineStr">
-        <is>
-          <t>Lost &amp; found</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AG12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>46111.53194444445</v>
+        <v>46111.64236111111</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46111.53402777778</v>
+        <v>46111.64444444444</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>sam.rivera@conestogac.on.ca</t>
+          <t>priya.singh@conestogac.on.ca</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sam Rivera</t>
+          <t>Priya Singh</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1888,20 +1876,20 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Afternoon (12 – 4pm)</t>
+          <t>Afternoon (12 – close)</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1910,10 +1898,10 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -1922,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1973,54 +1961,54 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="n">
-        <v>46111.64236111111</v>
+        <v>46111.73402777778</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46111.64444444444</v>
+        <v>46111.73680555556</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>priya.singh@conestogac.on.ca</t>
+          <t>fatima.khan@conestogac.on.ca</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Priya Singh</t>
+          <t>Fatima Khan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Doon</t>
+          <t>Waterloo</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Afternoon (12 – 4pm)</t>
+          <t>Afternoon (12 – close)</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I14" t="n">
         <v>4</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -2032,16 +2020,16 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
@@ -2062,7 +2050,7 @@
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2071,33 +2059,37 @@
         <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>Power outlet location</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="1" t="n">
-        <v>46114.45</v>
+        <v>46113.33541666667</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46114.45208333333</v>
+        <v>46113.33680555555</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>jordan.lee@conestogac.on.ca</t>
+          <t>priya.singh@conestogac.on.ca</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Jordan Lee</t>
+          <t>Priya Singh</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cambridge</t>
+          <t>Doon</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2106,58 +2098,58 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
         <v>3</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>3</v>
-      </c>
-      <c r="M15" t="n">
-        <v>2</v>
-      </c>
-      <c r="N15" t="n">
-        <v>3</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>2</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
       <c r="Y15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
@@ -2169,13 +2161,13 @@
         <v>2</v>
       </c>
       <c r="AC15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -2187,42 +2179,42 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="n">
-        <v>46115.60625</v>
+        <v>46113.53472222222</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46115.60833333333</v>
+        <v>46113.5375</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>fatima.khan@conestogac.on.ca</t>
+          <t>lucas.tremblay@conestogac.on.ca</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fatima Khan</t>
+          <t>Lucas Tremblay</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Reuter</t>
+          <t>Doon</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Afternoon (12 – 4pm)</t>
+          <t>Afternoon (12 – close)</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2252,19 +2244,19 @@
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z16" t="n">
         <v>0</v>
@@ -2273,7 +2265,7 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2294,10 +2286,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="n">
-        <v>46115.63333333333</v>
+        <v>46114.62708333333</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46115.63680555556</v>
+        <v>46114.62986111111</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2311,25 +2303,25 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Doon</t>
+          <t>Waterloo</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Afternoon (12 – 4pm)</t>
+          <t>Afternoon (12 – close)</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="I17" t="n">
         <v>11</v>
       </c>
       <c r="J17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2338,7 +2330,7 @@
         <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2350,16 +2342,16 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -2401,51 +2393,51 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="n">
-        <v>46117.33402777778</v>
+        <v>46114.70694444444</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46117.33611111111</v>
+        <v>46114.71041666667</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>sam.rivera@conestogac.on.ca</t>
+          <t>fatima.khan@conestogac.on.ca</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sam Rivera</t>
+          <t>Fatima Khan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cambridge</t>
+          <t>Waterloo</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Morning (open – 12pm)</t>
+          <t>Afternoon (12 – close)</t>
         </is>
       </c>
       <c r="H18" t="n">
+        <v>8</v>
+      </c>
+      <c r="I18" t="n">
         <v>6</v>
       </c>
-      <c r="I18" t="n">
-        <v>4</v>
-      </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2460,7 +2452,7 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
         <v>0</v>
@@ -2478,7 +2470,7 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z18" t="n">
         <v>0</v>
@@ -2508,45 +2500,45 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="n">
-        <v>46117.40416666667</v>
+        <v>46115.60625</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46117.40625</v>
+        <v>46115.60833333333</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>priya.singh@conestogac.on.ca</t>
+          <t>fatima.khan@conestogac.on.ca</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Priya Singh</t>
+          <t>Fatima Khan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Waterloo</t>
+          <t>Reuter</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Morning (open – 12pm)</t>
+          <t>Afternoon (12 – close)</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2558,7 +2550,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -2579,7 +2571,7 @@
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -2615,36 +2607,36 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="n">
-        <v>46120.70625</v>
+        <v>46117.33402777778</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46120.70902777778</v>
+        <v>46117.33611111111</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>aaron.chen@conestogac.on.ca</t>
+          <t>sam.rivera@conestogac.on.ca</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aaron Chen</t>
+          <t>Sam Rivera</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Waterloo</t>
+          <t>Cambridge</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Evening (4pm – close)</t>
+          <t>Morning (open – 12pm)</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2656,10 +2648,10 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2674,22 +2666,22 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
@@ -2707,38 +2699,34 @@
         <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG20" t="inlineStr">
-        <is>
-          <t>Power outlet location</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AG20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>20</v>
       </c>
       <c r="B21" s="1" t="n">
-        <v>46124.51458333333</v>
+        <v>46117.40416666667</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46124.51736111111</v>
+        <v>46117.40625</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>sam.rivera@conestogac.on.ca</t>
+          <t>priya.singh@conestogac.on.ca</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sam Rivera</t>
+          <t>Priya Singh</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2748,44 +2736,44 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Afternoon (12 – 4pm)</t>
+          <t>Morning (open – 12pm)</t>
         </is>
       </c>
       <c r="H21" t="n">
         <v>14</v>
       </c>
       <c r="I21" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
@@ -2833,51 +2821,51 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="n">
-        <v>46124.57013888889</v>
+        <v>46118.43680555555</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>46124.57291666666</v>
+        <v>46118.43819444445</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>lucas.tremblay@conestogac.on.ca</t>
+          <t>maya.patel@conestogac.on.ca</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lucas Tremblay</t>
+          <t>Maya Patel</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cambridge</t>
+          <t>Waterloo</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Afternoon (12 – 4pm)</t>
+          <t>Morning (open – 12pm)</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I22" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -2889,7 +2877,7 @@
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -2901,7 +2889,7 @@
         <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
@@ -2928,26 +2916,22 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF22" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG22" t="inlineStr">
-        <is>
-          <t>Tour request</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AG22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
         <v>22</v>
       </c>
       <c r="B23" s="1" t="n">
-        <v>46125.48680555556</v>
+        <v>46121.35833333333</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46125.48888888889</v>
+        <v>46121.36180555556</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2961,7 +2945,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Reuter</t>
+          <t>Doon</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2970,31 +2954,31 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I23" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="J23" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -3027,7 +3011,7 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
@@ -3051,36 +3035,36 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="n">
-        <v>46125.49583333333</v>
+        <v>46124.57013888889</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>46125.49791666667</v>
+        <v>46124.57291666666</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>fatima.khan@conestogac.on.ca</t>
+          <t>lucas.tremblay@conestogac.on.ca</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Fatima Khan</t>
+          <t>Lucas Tremblay</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Waterloo</t>
+          <t>Cambridge</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Morning (open – 12pm)</t>
+          <t>Afternoon (12 – close)</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3089,16 +3073,16 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
@@ -3107,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -3134,10 +3118,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3149,19 +3133,23 @@
         <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG24" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>Tour request</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
         <v>24</v>
       </c>
       <c r="B25" s="1" t="n">
-        <v>46125.55138888889</v>
+        <v>46125.38472222222</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>46125.55277777778</v>
+        <v>46125.38611111111</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3180,7 +3168,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Afternoon (12 – 4pm)</t>
+          <t>Morning (open – 12pm)</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -3265,54 +3253,54 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="n">
-        <v>46125.81944444445</v>
+        <v>46125.60694444444</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46125.82222222222</v>
+        <v>46125.60833333333</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>aaron.chen@conestogac.on.ca</t>
+          <t>priya.singh@conestogac.on.ca</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aaron Chen</t>
+          <t>Priya Singh</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Cambridge</t>
+          <t>Doon</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Evening (4pm – close)</t>
+          <t>Afternoon (12 – close)</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I26" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -3336,7 +3324,7 @@
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
         <v>0</v>
@@ -3372,63 +3360,63 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="n">
-        <v>46126.33194444444</v>
+        <v>46125.77361111111</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>46126.33541666667</v>
+        <v>46125.77708333333</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>lucas.tremblay@conestogac.on.ca</t>
+          <t>jordan.lee@conestogac.on.ca</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Lucas Tremblay</t>
+          <t>Jordan Lee</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cambridge</t>
+          <t>Doon</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Morning (open – 12pm)</t>
+          <t>Afternoon (12 – close)</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="I27" t="n">
+        <v>7</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" t="n">
         <v>3</v>
       </c>
-      <c r="J27" t="n">
-        <v>2</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
       <c r="L27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -3443,22 +3431,22 @@
         <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y27" t="n">
         <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3479,10 +3467,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="n">
-        <v>46126.60694444444</v>
+        <v>46126.33194444444</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>46126.61041666667</v>
+        <v>46126.33541666667</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3496,19 +3484,19 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Reuter</t>
+          <t>Cambridge</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Afternoon (12 – 4pm)</t>
+          <t>Morning (open – 12pm)</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="I28" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="J28" t="n">
         <v>2</v>
@@ -3517,13 +3505,13 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3532,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -3559,7 +3547,7 @@
         <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -3586,51 +3574,51 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="n">
-        <v>46126.70347222222</v>
+        <v>46126.33263888889</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46126.70694444444</v>
+        <v>46126.33541666667</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>sam.rivera@conestogac.on.ca</t>
+          <t>lucas.tremblay@conestogac.on.ca</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sam Rivera</t>
+          <t>Lucas Tremblay</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Cambridge</t>
+          <t>Waterloo</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Evening (4pm – close)</t>
+          <t>Morning (open – 12pm)</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="I29" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3654,7 +3642,7 @@
         <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W29" t="n">
         <v>2</v>
@@ -3663,7 +3651,7 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
@@ -3672,10 +3660,10 @@
         <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
         <v>0</v>
@@ -3693,54 +3681,54 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="n">
-        <v>46132.57291666666</v>
+        <v>46126.53680555556</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46132.57430555556</v>
+        <v>46126.54027777778</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>aaron.chen@conestogac.on.ca</t>
+          <t>sam.rivera@conestogac.on.ca</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aaron Chen</t>
+          <t>Sam Rivera</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Waterloo</t>
+          <t>Cambridge</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Afternoon (12 – 4pm)</t>
+          <t>Afternoon (12 – close)</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="I30" t="n">
+        <v>12</v>
+      </c>
+      <c r="J30" t="n">
+        <v>4</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2</v>
+      </c>
+      <c r="L30" t="n">
         <v>3</v>
       </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>2</v>
-      </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
         <v>0</v>
@@ -3749,7 +3737,7 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -3761,16 +3749,16 @@
         <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X30" t="n">
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z30" t="n">
         <v>0</v>
@@ -3782,10 +3770,10 @@
         <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -3800,19 +3788,19 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="n">
-        <v>46132.59097222222</v>
+        <v>46126.69236111111</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>46132.59236111111</v>
+        <v>46126.69513888889</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>jordan.lee@conestogac.on.ca</t>
+          <t>lucas.tremblay@conestogac.on.ca</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Jordan Lee</t>
+          <t>Lucas Tremblay</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3822,20 +3810,20 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Afternoon (12 – 4pm)</t>
+          <t>Afternoon (12 – close)</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="I31" t="n">
         <v>10</v>
       </c>
       <c r="J31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -3844,19 +3832,19 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -3865,13 +3853,13 @@
         <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
         <v>0</v>
@@ -3892,7 +3880,7 @@
         <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -3907,42 +3895,42 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="n">
-        <v>46132.6</v>
+        <v>46128.59583333333</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46132.60347222222</v>
+        <v>46128.59722222222</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>sam.rivera@conestogac.on.ca</t>
+          <t>priya.singh@conestogac.on.ca</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sam Rivera</t>
+          <t>Priya Singh</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Reuter</t>
+          <t>Cambridge</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Afternoon (12 – 4pm)</t>
+          <t>Afternoon (12 – close)</t>
         </is>
       </c>
       <c r="H32" t="n">
         <v>6</v>
       </c>
       <c r="I32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -3951,7 +3939,7 @@
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -3981,7 +3969,7 @@
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y32" t="n">
         <v>0</v>
@@ -3990,7 +3978,7 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
         <v>2</v>
@@ -4014,57 +4002,57 @@
         <v>32</v>
       </c>
       <c r="B33" s="1" t="n">
-        <v>46132.65833333333</v>
+        <v>46132.55416666667</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46132.66111111111</v>
+        <v>46132.55763888889</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>aaron.chen@conestogac.on.ca</t>
+          <t>fatima.khan@conestogac.on.ca</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aaron Chen</t>
+          <t>Fatima Khan</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Doon</t>
+          <t>Cambridge</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Afternoon (12 – 4pm)</t>
+          <t>Afternoon (12 – close)</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J33" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -4085,13 +4073,13 @@
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z33" t="n">
         <v>0</v>
@@ -4121,63 +4109,63 @@
         <v>33</v>
       </c>
       <c r="B34" s="1" t="n">
-        <v>46136.75555555556</v>
+        <v>46132.59097222222</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>46136.75902777778</v>
+        <v>46132.59236111111</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>maya.patel@conestogac.on.ca</t>
+          <t>jordan.lee@conestogac.on.ca</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Maya Patel</t>
+          <t>Jordan Lee</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Doon</t>
+          <t>Reuter</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Evening (4pm – close)</t>
+          <t>Afternoon (12 – close)</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K34" t="n">
         <v>3</v>
       </c>
       <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
         <v>3</v>
       </c>
-      <c r="M34" t="n">
-        <v>2</v>
-      </c>
-      <c r="N34" t="n">
-        <v>1</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q34" t="n">
         <v>1</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -4186,13 +4174,13 @@
         <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X34" t="n">
         <v>0</v>
@@ -4228,10 +4216,10 @@
         <v>34</v>
       </c>
       <c r="B35" s="1" t="n">
-        <v>46138.59791666667</v>
+        <v>46139.35416666666</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>46138.60138888889</v>
+        <v>46139.35763888889</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4245,34 +4233,34 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Doon</t>
+          <t>Waterloo</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Afternoon (12 – 4pm)</t>
+          <t>Morning (open – 12pm)</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J35" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4311,7 +4299,7 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
         <v>0</v>
@@ -4442,10 +4430,10 @@
         <v>36</v>
       </c>
       <c r="B37" s="1" t="n">
-        <v>46140.47777777778</v>
+        <v>46139.58611111111</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46140.48055555556</v>
+        <v>46139.58958333333</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4459,46 +4447,46 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Cambridge</t>
+          <t>Doon</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Morning (open – 12pm)</t>
+          <t>Afternoon (12 – close)</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I37" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -4528,7 +4516,7 @@
         <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4540,57 +4528,61 @@
         <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG37" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>Power outlet location</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
         <v>37</v>
       </c>
       <c r="B38" s="1" t="n">
-        <v>46140.50972222222</v>
+        <v>46142.56944444445</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>46140.51319444444</v>
+        <v>46142.57291666666</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>lucas.tremblay@conestogac.on.ca</t>
+          <t>maya.patel@conestogac.on.ca</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Lucas Tremblay</t>
+          <t>Maya Patel</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Reuter</t>
+          <t>Waterloo</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Afternoon (12 – 4pm)</t>
+          <t>Afternoon (12 – close)</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I38" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K38" t="n">
         <v>2</v>
       </c>
       <c r="L38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
@@ -4599,16 +4591,16 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
         <v>0</v>
@@ -4626,7 +4618,7 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
         <v>0</v>
@@ -4656,36 +4648,36 @@
         <v>38</v>
       </c>
       <c r="B39" s="1" t="n">
-        <v>46141.62361111111</v>
+        <v>46146.45833333334</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>46141.62638888889</v>
+        <v>46146.46041666667</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>fatima.khan@conestogac.on.ca</t>
+          <t>lucas.tremblay@conestogac.on.ca</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Fatima Khan</t>
+          <t>Lucas Tremblay</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Waterloo</t>
+          <t>Doon</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Afternoon (12 – 4pm)</t>
+          <t>Morning (open – 12pm)</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I39" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>2</v>
@@ -4694,7 +4686,7 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -4754,57 +4746,61 @@
         <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG39" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>Power outlet location</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
         <v>39</v>
       </c>
       <c r="B40" s="1" t="n">
-        <v>46142.55486111111</v>
+        <v>46146.66458333333</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>46142.55763888889</v>
+        <v>46146.66736111111</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>sam.rivera@conestogac.on.ca</t>
+          <t>lucas.tremblay@conestogac.on.ca</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sam Rivera</t>
+          <t>Lucas Tremblay</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Doon</t>
+          <t>Reuter</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Afternoon (12 – 4pm)</t>
+          <t>Afternoon (12 – close)</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
@@ -4813,10 +4809,10 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
@@ -4825,13 +4821,13 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
         <v>0</v>
@@ -4849,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE40" t="n">
         <v>0</v>
@@ -4870,19 +4866,19 @@
         <v>40</v>
       </c>
       <c r="B41" s="1" t="n">
-        <v>46146.45833333334</v>
+        <v>46146.74930555555</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>46146.46041666667</v>
+        <v>46146.75069444445</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>lucas.tremblay@conestogac.on.ca</t>
+          <t>priya.singh@conestogac.on.ca</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Lucas Tremblay</t>
+          <t>Priya Singh</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4892,23 +4888,23 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Morning (open – 12pm)</t>
+          <t>Afternoon (12 – close)</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
@@ -4929,7 +4925,7 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T41" t="n">
         <v>0</v>
@@ -4944,7 +4940,7 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y41" t="n">
         <v>0</v>
@@ -4968,13 +4964,9 @@
         <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG41" t="inlineStr">
-        <is>
-          <t>Power outlet location</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AG41" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
